--- a/Estimacion_error/datos_aves_marinas/2026/abril/RLOF/conteos_reales.xlsx
+++ b/Estimacion_error/datos_aves_marinas/2026/abril/RLOF/conteos_reales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renzo\Desktop\Data_Saiensss\Estadística\Trabajos (laborales)\BMAP\Proyectos\conteo-aves-bmap\Estimacion_error\datos_aves_marinas\2026\abril\RLOF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA09AAD2-AF50-49F1-BAB2-ACA6C2662A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09044B1-12D1-4710-B5D1-3BB0B80AD1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$F$3:$L$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$127</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="20">
   <si>
     <t>FOTO</t>
   </si>
@@ -92,6 +93,12 @@
   </si>
   <si>
     <t>MAE</t>
+  </si>
+  <si>
+    <t>sMAPE</t>
+  </si>
+  <si>
+    <t>Smape</t>
   </si>
 </sst>
 </file>
@@ -1896,10 +1903,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F58841F4-1925-4FDA-9F67-00E3EE1323CD}">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1910,7 +1917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>764</v>
       </c>
@@ -1921,7 +1928,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>772</v>
       </c>
@@ -1949,8 +1956,11 @@
       <c r="K3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>775</v>
       </c>
@@ -1961,28 +1971,32 @@
         <v>169</v>
       </c>
       <c r="F4">
-        <v>959</v>
+        <v>846</v>
       </c>
       <c r="G4" t="s">
         <v>3</v>
       </c>
       <c r="H4">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="I4">
         <f>VLOOKUP(F4,$A$1:$C$45,3,0)</f>
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <f>H4-I4</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <f>ABS(J4)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <f>K4/(H4+I4)*2</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>784</v>
       </c>
@@ -1993,28 +2007,32 @@
         <v>175</v>
       </c>
       <c r="F5">
-        <v>962</v>
+        <v>870</v>
       </c>
       <c r="G5" t="s">
         <v>3</v>
       </c>
       <c r="H5">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="I5">
-        <f t="shared" ref="I5:I9" si="0">VLOOKUP(F5,$A$1:$C$45,3,0)</f>
-        <v>61</v>
+        <f>VLOOKUP(F5,$A$1:$C$45,3,0)</f>
+        <v>70</v>
       </c>
       <c r="J5">
-        <f t="shared" ref="J5:J9" si="1">H5-I5</f>
-        <v>-10</v>
+        <f t="shared" ref="J5:J29" si="0">H5-I5</f>
+        <v>6</v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:K9" si="2">ABS(J5)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ref="K5:K29" si="1">ABS(J5)</f>
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ref="L5:L29" si="2">K5/(H5+I5)*2</f>
+        <v>8.2191780821917804E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>788</v>
       </c>
@@ -2025,28 +2043,39 @@
         <v>134</v>
       </c>
       <c r="F6">
-        <v>965</v>
+        <v>877</v>
       </c>
       <c r="G6" t="s">
         <v>3</v>
       </c>
       <c r="H6">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="I6">
+        <f>VLOOKUP(F6,$A$1:$C$45,3,0)</f>
+        <v>63</v>
+      </c>
+      <c r="J6">
         <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="1"/>
-        <v>-11</v>
-      </c>
-      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O6">
+        <f>AVERAGE(K4:K29)</f>
+        <v>7.384615384615385</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>793</v>
       </c>
@@ -2057,264 +2086,603 @@
         <v>167</v>
       </c>
       <c r="F7">
-        <v>968</v>
+        <v>879</v>
       </c>
       <c r="G7" t="s">
         <v>3</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I7">
+        <f>VLOOKUP(F7,$A$1:$C$45,3,0)</f>
+        <v>24</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="2"/>
+        <v>0.08</v>
+      </c>
+      <c r="N7" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <f>AVERAGE(L4:L29)</f>
+        <v>0.35876637664559285</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>799</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>182</v>
+      </c>
+      <c r="F8">
+        <v>882</v>
+      </c>
+      <c r="G8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>35</v>
+      </c>
+      <c r="I8">
+        <f>VLOOKUP(F8,$A$1:$C$45,3,0)</f>
+        <v>27</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="2"/>
+        <v>0.25806451612903225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>804</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>218</v>
+      </c>
+      <c r="F9">
+        <v>885</v>
+      </c>
+      <c r="H9">
+        <v>14</v>
+      </c>
+      <c r="I9">
+        <f>VLOOKUP(F9,$A$1:$C$45,3,0)</f>
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>808</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>161</v>
+      </c>
+      <c r="F10">
+        <v>890</v>
+      </c>
+      <c r="H10">
+        <v>41</v>
+      </c>
+      <c r="I10">
+        <f>VLOOKUP(F10,$A$1:$C$45,3,0)</f>
+        <v>27</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>0.41176470588235292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>813</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>234</v>
+      </c>
+      <c r="F11">
+        <v>899</v>
+      </c>
+      <c r="H11">
+        <v>72</v>
+      </c>
+      <c r="I11">
+        <f>VLOOKUP(F11,$A$1:$C$45,3,0)</f>
+        <v>71</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>1.3986013986013986E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>818</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>254</v>
+      </c>
+      <c r="F12">
+        <v>903</v>
+      </c>
+      <c r="H12">
+        <v>111</v>
+      </c>
+      <c r="I12">
+        <f>VLOOKUP(F12,$A$1:$C$45,3,0)</f>
+        <v>102</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>8.4507042253521125E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>823</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>174</v>
+      </c>
+      <c r="F13">
+        <v>907</v>
+      </c>
+      <c r="H13">
+        <v>107</v>
+      </c>
+      <c r="I13">
+        <f>VLOOKUP(F13,$A$1:$C$45,3,0)</f>
+        <v>109</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="2"/>
+        <v>1.8518518518518517E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>828</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>228</v>
+      </c>
+      <c r="F14">
+        <v>910</v>
+      </c>
+      <c r="H14">
+        <v>42</v>
+      </c>
+      <c r="I14">
+        <f>VLOOKUP(F14,$A$1:$C$45,3,0)</f>
+        <v>55</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>-13</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="2"/>
+        <v>0.26804123711340205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>833</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>220</v>
+      </c>
+      <c r="F15">
+        <v>913</v>
+      </c>
+      <c r="H15">
+        <v>12</v>
+      </c>
+      <c r="I15">
+        <f>VLOOKUP(F15,$A$1:$C$45,3,0)</f>
+        <v>13</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="2"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>837</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>117</v>
+      </c>
+      <c r="F16">
+        <v>936</v>
+      </c>
+      <c r="H16">
+        <v>209</v>
+      </c>
+      <c r="I16">
+        <f>VLOOKUP(F16,$A$1:$C$45,3,0)</f>
+        <v>174</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="2"/>
+        <v>0.18276762402088773</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>846</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>938</v>
+      </c>
+      <c r="H17">
+        <v>78</v>
+      </c>
+      <c r="I17">
+        <f>VLOOKUP(F17,$A$1:$C$45,3,0)</f>
+        <v>72</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="2"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>846</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>11</v>
+      </c>
+      <c r="F18">
+        <v>940</v>
+      </c>
+      <c r="H18">
+        <v>34</v>
+      </c>
+      <c r="I18">
+        <f>VLOOKUP(F18,$A$1:$C$45,3,0)</f>
+        <v>40</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>-6</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="2"/>
+        <v>0.16216216216216217</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>870</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>70</v>
+      </c>
+      <c r="F19">
+        <v>944</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <f>VLOOKUP(F19,$A$1:$C$45,3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="2"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>877</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>63</v>
+      </c>
+      <c r="F20">
+        <v>946</v>
+      </c>
+      <c r="H20">
+        <v>22</v>
+      </c>
+      <c r="I20">
+        <f>VLOOKUP(F20,$A$1:$C$45,3,0)</f>
+        <v>31</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="0"/>
+        <v>-9</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="2"/>
+        <v>0.33962264150943394</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>879</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>24</v>
+      </c>
+      <c r="F21">
+        <v>947</v>
+      </c>
+      <c r="H21">
+        <v>63</v>
+      </c>
+      <c r="I21">
+        <f>VLOOKUP(F21,$A$1:$C$45,3,0)</f>
+        <v>69</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="0"/>
+        <v>-6</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="2"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>882</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22">
+        <v>27</v>
+      </c>
+      <c r="F22">
+        <v>953</v>
+      </c>
+      <c r="H22">
+        <v>11</v>
+      </c>
+      <c r="I22">
+        <f>VLOOKUP(F22,$A$1:$C$45,3,0)</f>
+        <v>10</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="2"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>885</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>11</v>
+      </c>
+      <c r="F23">
+        <v>954</v>
+      </c>
+      <c r="H23">
+        <v>43</v>
+      </c>
+      <c r="I23">
+        <f>VLOOKUP(F23,$A$1:$C$45,3,0)</f>
+        <v>40</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="2"/>
+        <v>7.2289156626506021E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>890</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>27</v>
+      </c>
+      <c r="F24">
+        <v>959</v>
+      </c>
+      <c r="H24">
+        <v>78</v>
+      </c>
+      <c r="I24">
+        <f>VLOOKUP(F24,$A$1:$C$45,3,0)</f>
+        <v>63</v>
+      </c>
+      <c r="J24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="J7">
+      <c r="K24">
         <f t="shared" si="1"/>
-        <v>-12</v>
-      </c>
-      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L24">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>799</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>182</v>
-      </c>
-      <c r="F8">
-        <v>993</v>
-      </c>
-      <c r="G8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="1"/>
-        <v>-3</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>804</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9">
-        <v>218</v>
-      </c>
-      <c r="F9">
-        <v>997</v>
-      </c>
-      <c r="G9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="1"/>
-        <v>-10</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>808</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>813</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>818</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>823</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>174</v>
-      </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13">
-        <f>AVERAGE(K4:K9)</f>
-        <v>10.166666666666666</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>828</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>833</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>837</v>
-      </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>846</v>
-      </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>846</v>
-      </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>870</v>
-      </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>877</v>
-      </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>879</v>
-      </c>
-      <c r="B21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>882</v>
-      </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>885</v>
-      </c>
-      <c r="B23" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>890</v>
-      </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.21276595744680851</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>899</v>
       </c>
@@ -2324,8 +2692,30 @@
       <c r="C25">
         <v>71</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <v>962</v>
+      </c>
+      <c r="H25">
+        <v>51</v>
+      </c>
+      <c r="I25">
+        <f>VLOOKUP(F25,$A$1:$C$45,3,0)</f>
+        <v>61</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="0"/>
+        <v>-10</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="2"/>
+        <v>0.17857142857142858</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>903</v>
       </c>
@@ -2335,8 +2725,30 @@
       <c r="C26">
         <v>102</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <v>965</v>
+      </c>
+      <c r="H26">
+        <v>30</v>
+      </c>
+      <c r="I26">
+        <f>VLOOKUP(F26,$A$1:$C$45,3,0)</f>
+        <v>41</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="0"/>
+        <v>-11</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="2"/>
+        <v>0.30985915492957744</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>907</v>
       </c>
@@ -2346,8 +2758,30 @@
       <c r="C27">
         <v>109</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <v>968</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <f>VLOOKUP(F27,$A$1:$C$45,3,0)</f>
+        <v>15</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="0"/>
+        <v>-12</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="2"/>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>910</v>
       </c>
@@ -2357,8 +2791,30 @@
       <c r="C28">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <v>993</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <f>VLOOKUP(F28,$A$1:$C$45,3,0)</f>
+        <v>3</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>913</v>
       </c>
@@ -2368,8 +2824,30 @@
       <c r="C29">
         <v>13</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <v>997</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <f>VLOOKUP(F29,$A$1:$C$45,3,0)</f>
+        <v>11</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="0"/>
+        <v>-10</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="2"/>
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>936</v>
       </c>
@@ -2380,7 +2858,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>938</v>
       </c>
@@ -2391,7 +2869,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>940</v>
       </c>
@@ -2546,6 +3024,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="F3:L29" xr:uid="{F58841F4-1925-4FDA-9F67-00E3EE1323CD}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Estimacion_error/datos_aves_marinas/2026/abril/RLOF/conteos_reales.xlsx
+++ b/Estimacion_error/datos_aves_marinas/2026/abril/RLOF/conteos_reales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renzo\Desktop\Data_Saiensss\Estadística\Trabajos (laborales)\BMAP\Proyectos\conteo-aves-bmap\Estimacion_error\datos_aves_marinas\2026\abril\RLOF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renzo\Desktop\Estadística\Trabajos (laborales)\BMAP\Proyectos\conteo-aves-bmap\Estimacion_error\datos_aves_marinas\2026\abril\RLOF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09044B1-12D1-4710-B5D1-3BB0B80AD1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F55D47-421A-4CC2-A71B-4F5626E435C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="20">
   <si>
     <t>FOTO</t>
   </si>
@@ -83,9 +80,6 @@
     <t>Gaviota dominicana adulto</t>
   </si>
   <si>
-    <t>x_0.20</t>
-  </si>
-  <si>
     <t>Error</t>
   </si>
   <si>
@@ -100,11 +94,17 @@
   <si>
     <t>Smape</t>
   </si>
+  <si>
+    <t>x_0.21</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -142,11 +142,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -165,9 +166,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -205,9 +206,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -240,26 +241,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -292,26 +276,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -485,14 +452,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:C127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,7 +469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>764</v>
       </c>
@@ -514,7 +480,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>772</v>
       </c>
@@ -525,7 +491,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>772</v>
       </c>
@@ -536,7 +502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>772</v>
       </c>
@@ -547,7 +513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>775</v>
       </c>
@@ -558,7 +524,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>784</v>
       </c>
@@ -569,7 +535,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>784</v>
       </c>
@@ -580,7 +546,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>784</v>
       </c>
@@ -591,7 +557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>788</v>
       </c>
@@ -602,7 +568,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>788</v>
       </c>
@@ -613,7 +579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>793</v>
       </c>
@@ -624,7 +590,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>793</v>
       </c>
@@ -635,7 +601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>799</v>
       </c>
@@ -646,7 +612,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>799</v>
       </c>
@@ -657,7 +623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>804</v>
       </c>
@@ -668,7 +634,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>804</v>
       </c>
@@ -679,7 +645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>808</v>
       </c>
@@ -690,7 +656,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>808</v>
       </c>
@@ -701,7 +667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>813</v>
       </c>
@@ -712,7 +678,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>813</v>
       </c>
@@ -723,7 +689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>813</v>
       </c>
@@ -734,7 +700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>818</v>
       </c>
@@ -745,7 +711,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>818</v>
       </c>
@@ -756,7 +722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>823</v>
       </c>
@@ -767,7 +733,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>823</v>
       </c>
@@ -778,7 +744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>823</v>
       </c>
@@ -789,7 +755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>828</v>
       </c>
@@ -800,7 +766,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>828</v>
       </c>
@@ -811,7 +777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>828</v>
       </c>
@@ -822,7 +788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>833</v>
       </c>
@@ -833,7 +799,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>833</v>
       </c>
@@ -844,7 +810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>837</v>
       </c>
@@ -855,7 +821,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>837</v>
       </c>
@@ -866,7 +832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>837</v>
       </c>
@@ -877,7 +843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>846</v>
       </c>
@@ -888,7 +854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>846</v>
       </c>
@@ -899,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>846</v>
       </c>
@@ -910,7 +876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>846</v>
       </c>
@@ -921,7 +887,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>862</v>
       </c>
@@ -932,7 +898,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>862</v>
       </c>
@@ -943,7 +909,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>870</v>
       </c>
@@ -954,7 +920,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>870</v>
       </c>
@@ -965,7 +931,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>870</v>
       </c>
@@ -976,7 +942,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>870</v>
       </c>
@@ -987,7 +953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>877</v>
       </c>
@@ -998,7 +964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>877</v>
       </c>
@@ -1009,7 +975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>877</v>
       </c>
@@ -1020,7 +986,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>877</v>
       </c>
@@ -1031,7 +997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>879</v>
       </c>
@@ -1042,7 +1008,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>879</v>
       </c>
@@ -1053,7 +1019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>879</v>
       </c>
@@ -1064,7 +1030,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>882</v>
       </c>
@@ -1075,7 +1041,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>882</v>
       </c>
@@ -1086,7 +1052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>882</v>
       </c>
@@ -1097,7 +1063,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>882</v>
       </c>
@@ -1108,7 +1074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>882</v>
       </c>
@@ -1119,7 +1085,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>885</v>
       </c>
@@ -1130,7 +1096,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>885</v>
       </c>
@@ -1141,7 +1107,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>885</v>
       </c>
@@ -1152,7 +1118,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>885</v>
       </c>
@@ -1163,7 +1129,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>890</v>
       </c>
@@ -1174,7 +1140,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>890</v>
       </c>
@@ -1185,7 +1151,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>890</v>
       </c>
@@ -1196,7 +1162,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>890</v>
       </c>
@@ -1207,7 +1173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>890</v>
       </c>
@@ -1218,7 +1184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>893</v>
       </c>
@@ -1229,7 +1195,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>899</v>
       </c>
@@ -1240,7 +1206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>899</v>
       </c>
@@ -1251,7 +1217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>899</v>
       </c>
@@ -1262,7 +1228,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>899</v>
       </c>
@@ -1273,7 +1239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>899</v>
       </c>
@@ -1284,7 +1250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>903</v>
       </c>
@@ -1295,7 +1261,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>903</v>
       </c>
@@ -1306,7 +1272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>903</v>
       </c>
@@ -1317,7 +1283,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>903</v>
       </c>
@@ -1328,7 +1294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>907</v>
       </c>
@@ -1339,7 +1305,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>907</v>
       </c>
@@ -1350,7 +1316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>910</v>
       </c>
@@ -1361,7 +1327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>910</v>
       </c>
@@ -1372,7 +1338,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>910</v>
       </c>
@@ -1383,7 +1349,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>913</v>
       </c>
@@ -1394,7 +1360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>917</v>
       </c>
@@ -1405,7 +1371,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>927</v>
       </c>
@@ -1416,7 +1382,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>936</v>
       </c>
@@ -1427,7 +1393,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>936</v>
       </c>
@@ -1438,7 +1404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>936</v>
       </c>
@@ -1449,7 +1415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>938</v>
       </c>
@@ -1460,7 +1426,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>938</v>
       </c>
@@ -1471,7 +1437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>938</v>
       </c>
@@ -1482,7 +1448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>940</v>
       </c>
@@ -1493,7 +1459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>940</v>
       </c>
@@ -1504,7 +1470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>940</v>
       </c>
@@ -1515,7 +1481,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>940</v>
       </c>
@@ -1526,7 +1492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>944</v>
       </c>
@@ -1537,7 +1503,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>944</v>
       </c>
@@ -1548,7 +1514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>944</v>
       </c>
@@ -1559,7 +1525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>946</v>
       </c>
@@ -1570,7 +1536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>946</v>
       </c>
@@ -1581,7 +1547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>946</v>
       </c>
@@ -1592,7 +1558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>946</v>
       </c>
@@ -1603,7 +1569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>947</v>
       </c>
@@ -1614,7 +1580,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>948</v>
       </c>
@@ -1625,7 +1591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>948</v>
       </c>
@@ -1636,7 +1602,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>950</v>
       </c>
@@ -1647,7 +1613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>950</v>
       </c>
@@ -1658,7 +1624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>953</v>
       </c>
@@ -1669,7 +1635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>953</v>
       </c>
@@ -1680,7 +1646,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>953</v>
       </c>
@@ -1691,7 +1657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>954</v>
       </c>
@@ -1702,7 +1668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>954</v>
       </c>
@@ -1713,7 +1679,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>959</v>
       </c>
@@ -1724,7 +1690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>959</v>
       </c>
@@ -1735,7 +1701,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>959</v>
       </c>
@@ -1746,7 +1712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>962</v>
       </c>
@@ -1757,7 +1723,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>962</v>
       </c>
@@ -1768,7 +1734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>965</v>
       </c>
@@ -1779,7 +1745,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>965</v>
       </c>
@@ -1790,7 +1756,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>965</v>
       </c>
@@ -1801,7 +1767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>968</v>
       </c>
@@ -1812,7 +1778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>968</v>
       </c>
@@ -1823,7 +1789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>970</v>
       </c>
@@ -1834,7 +1800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>970</v>
       </c>
@@ -1845,7 +1811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>983</v>
       </c>
@@ -1856,7 +1822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>993</v>
       </c>
@@ -1867,7 +1833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>997</v>
       </c>
@@ -1878,7 +1844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>997</v>
       </c>
@@ -1890,23 +1856,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C127" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="zarcillo"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:C127" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F58841F4-1925-4FDA-9F67-00E3EE1323CD}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="15" max="15" width="12.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1917,7 +1881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>764</v>
       </c>
@@ -1928,7 +1892,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>772</v>
       </c>
@@ -1945,22 +1909,22 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
         <v>2</v>
       </c>
       <c r="J3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" t="s">
         <v>15</v>
       </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
       <c r="L3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>775</v>
       </c>
@@ -1996,7 +1960,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>784</v>
       </c>
@@ -2013,7 +1977,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I5">
         <f>VLOOKUP(F5,$A$1:$C$45,3,0)</f>
@@ -2021,18 +1985,18 @@
       </c>
       <c r="J5">
         <f t="shared" ref="J5:J29" si="0">H5-I5</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:K29" si="1">ABS(J5)</f>
-        <v>6</v>
+        <f>ABS(J5)</f>
+        <v>3</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L5:L29" si="2">K5/(H5+I5)*2</f>
-        <v>8.2191780821917804E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" ref="L5:L29" si="1">K5/(H5+I5)*2</f>
+        <v>4.195804195804196E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>788</v>
       </c>
@@ -2060,22 +2024,22 @@
         <v>0</v>
       </c>
       <c r="K6">
+        <f>ABS(J6)</f>
+        <v>0</v>
+      </c>
+      <c r="L6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="N6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O6">
+        <v>16</v>
+      </c>
+      <c r="O6" s="2">
         <f>AVERAGE(K4:K29)</f>
-        <v>7.384615384615385</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>793</v>
       </c>
@@ -2103,22 +2067,22 @@
         <v>2</v>
       </c>
       <c r="K7">
+        <f>ABS(J7)</f>
+        <v>2</v>
+      </c>
+      <c r="L7">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
       <c r="N7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O7">
         <f>AVERAGE(L4:L29)</f>
-        <v>0.35876637664559285</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.35543593020983327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>799</v>
       </c>
@@ -2130,9 +2094,6 @@
       </c>
       <c r="F8">
         <v>882</v>
-      </c>
-      <c r="G8" t="s">
-        <v>3</v>
       </c>
       <c r="H8">
         <v>35</v>
@@ -2146,15 +2107,15 @@
         <v>8</v>
       </c>
       <c r="K8">
+        <f>ABS(J8)</f>
+        <v>8</v>
+      </c>
+      <c r="L8">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="2"/>
         <v>0.25806451612903225</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>804</v>
       </c>
@@ -2179,15 +2140,15 @@
         <v>3</v>
       </c>
       <c r="K9">
+        <f>ABS(J9)</f>
+        <v>3</v>
+      </c>
+      <c r="L9">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>808</v>
       </c>
@@ -2201,7 +2162,7 @@
         <v>890</v>
       </c>
       <c r="H10">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I10">
         <f>VLOOKUP(F10,$A$1:$C$45,3,0)</f>
@@ -2209,18 +2170,18 @@
       </c>
       <c r="J10">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K10">
+        <f>ABS(J10)</f>
+        <v>11</v>
+      </c>
+      <c r="L10">
         <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="2"/>
-        <v>0.41176470588235292</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.33846153846153848</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>813</v>
       </c>
@@ -2245,15 +2206,15 @@
         <v>1</v>
       </c>
       <c r="K11">
+        <f>ABS(J11)</f>
+        <v>1</v>
+      </c>
+      <c r="L11">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="2"/>
         <v>1.3986013986013986E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>818</v>
       </c>
@@ -2267,7 +2228,7 @@
         <v>903</v>
       </c>
       <c r="H12">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I12">
         <f>VLOOKUP(F12,$A$1:$C$45,3,0)</f>
@@ -2275,18 +2236,18 @@
       </c>
       <c r="J12">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K12">
+        <f>ABS(J12)</f>
+        <v>6</v>
+      </c>
+      <c r="L12">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="2"/>
-        <v>8.4507042253521125E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>5.7142857142857141E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>823</v>
       </c>
@@ -2300,7 +2261,7 @@
         <v>907</v>
       </c>
       <c r="H13">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I13">
         <f>VLOOKUP(F13,$A$1:$C$45,3,0)</f>
@@ -2308,18 +2269,18 @@
       </c>
       <c r="J13">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="K13">
+        <f>ABS(J13)</f>
+        <v>6</v>
+      </c>
+      <c r="L13">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="2"/>
-        <v>1.8518518518518517E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>5.6603773584905662E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>828</v>
       </c>
@@ -2333,7 +2294,7 @@
         <v>910</v>
       </c>
       <c r="H14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I14">
         <f>VLOOKUP(F14,$A$1:$C$45,3,0)</f>
@@ -2341,18 +2302,18 @@
       </c>
       <c r="J14">
         <f t="shared" si="0"/>
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="K14">
+        <f>ABS(J14)</f>
+        <v>14</v>
+      </c>
+      <c r="L14">
         <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="2"/>
-        <v>0.26804123711340205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.29166666666666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>833</v>
       </c>
@@ -2377,15 +2338,15 @@
         <v>-1</v>
       </c>
       <c r="K15">
+        <f>ABS(J15)</f>
+        <v>1</v>
+      </c>
+      <c r="L15">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>837</v>
       </c>
@@ -2399,7 +2360,7 @@
         <v>936</v>
       </c>
       <c r="H16">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="I16">
         <f>VLOOKUP(F16,$A$1:$C$45,3,0)</f>
@@ -2407,18 +2368,18 @@
       </c>
       <c r="J16">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K16">
+        <f>ABS(J16)</f>
+        <v>30</v>
+      </c>
+      <c r="L16">
         <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="L16">
-        <f t="shared" si="2"/>
-        <v>0.18276762402088773</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.15873015873015872</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>846</v>
       </c>
@@ -2432,7 +2393,7 @@
         <v>938</v>
       </c>
       <c r="H17">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I17">
         <f>VLOOKUP(F17,$A$1:$C$45,3,0)</f>
@@ -2440,18 +2401,18 @@
       </c>
       <c r="J17">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K17">
+        <f>ABS(J17)</f>
+        <v>3</v>
+      </c>
+      <c r="L17">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="2"/>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>4.0816326530612242E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>846</v>
       </c>
@@ -2476,15 +2437,15 @@
         <v>-6</v>
       </c>
       <c r="K18">
+        <f>ABS(J18)</f>
+        <v>6</v>
+      </c>
+      <c r="L18">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L18">
-        <f t="shared" si="2"/>
         <v>0.16216216216216217</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>870</v>
       </c>
@@ -2509,15 +2470,15 @@
         <v>-1</v>
       </c>
       <c r="K19">
+        <f>ABS(J19)</f>
+        <v>1</v>
+      </c>
+      <c r="L19">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="2"/>
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>877</v>
       </c>
@@ -2542,15 +2503,15 @@
         <v>-9</v>
       </c>
       <c r="K20">
+        <f>ABS(J20)</f>
+        <v>9</v>
+      </c>
+      <c r="L20">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="L20">
-        <f t="shared" si="2"/>
         <v>0.33962264150943394</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>879</v>
       </c>
@@ -2564,7 +2525,7 @@
         <v>947</v>
       </c>
       <c r="H21">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I21">
         <f>VLOOKUP(F21,$A$1:$C$45,3,0)</f>
@@ -2572,18 +2533,18 @@
       </c>
       <c r="J21">
         <f t="shared" si="0"/>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="K21">
+        <f>ABS(J21)</f>
+        <v>7</v>
+      </c>
+      <c r="L21">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L21">
-        <f t="shared" si="2"/>
-        <v>9.0909090909090912E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.10687022900763359</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>882</v>
       </c>
@@ -2608,15 +2569,15 @@
         <v>1</v>
       </c>
       <c r="K22">
+        <f>ABS(J22)</f>
+        <v>1</v>
+      </c>
+      <c r="L22">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <f t="shared" si="2"/>
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>885</v>
       </c>
@@ -2641,15 +2602,15 @@
         <v>3</v>
       </c>
       <c r="K23">
+        <f>ABS(J23)</f>
+        <v>3</v>
+      </c>
+      <c r="L23">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="2"/>
         <v>7.2289156626506021E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>890</v>
       </c>
@@ -2663,26 +2624,26 @@
         <v>959</v>
       </c>
       <c r="H24">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I24">
-        <f>VLOOKUP(F24,$A$1:$C$45,3,0)</f>
+        <f t="shared" ref="I24:I29" si="2">VLOOKUP(F24,$A$1:$C$45,3,0)</f>
         <v>63</v>
       </c>
       <c r="J24">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K24">
+        <f t="shared" ref="K24:K29" si="3">ABS(J24)</f>
+        <v>14</v>
+      </c>
+      <c r="L24">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L24">
-        <f t="shared" si="2"/>
-        <v>0.21276595744680851</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>899</v>
       </c>
@@ -2696,26 +2657,26 @@
         <v>962</v>
       </c>
       <c r="H25">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I25">
-        <f>VLOOKUP(F25,$A$1:$C$45,3,0)</f>
+        <f t="shared" si="2"/>
         <v>61</v>
       </c>
       <c r="J25">
         <f t="shared" si="0"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="K25">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="L25">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L25">
-        <f t="shared" si="2"/>
-        <v>0.17857142857142858</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.1981981981981982</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>903</v>
       </c>
@@ -2729,26 +2690,26 @@
         <v>965</v>
       </c>
       <c r="H26">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I26">
-        <f>VLOOKUP(F26,$A$1:$C$45,3,0)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="J26">
         <f t="shared" si="0"/>
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="K26">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="L26">
         <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="L26">
-        <f t="shared" si="2"/>
-        <v>0.30985915492957744</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.34285714285714286</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>907</v>
       </c>
@@ -2765,7 +2726,7 @@
         <v>3</v>
       </c>
       <c r="I27">
-        <f>VLOOKUP(F27,$A$1:$C$45,3,0)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="J27">
@@ -2773,15 +2734,15 @@
         <v>-12</v>
       </c>
       <c r="K27">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="L27">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="L27">
-        <f t="shared" si="2"/>
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>910</v>
       </c>
@@ -2798,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <f>VLOOKUP(F28,$A$1:$C$45,3,0)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="J28">
@@ -2806,15 +2767,15 @@
         <v>-3</v>
       </c>
       <c r="K28">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="L28">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="L28">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>913</v>
       </c>
@@ -2835,19 +2796,19 @@
         <v>11</v>
       </c>
       <c r="J29">
-        <f t="shared" si="0"/>
+        <f>H29-I29</f>
         <v>-10</v>
       </c>
       <c r="K29">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="L29">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L29">
-        <f t="shared" si="2"/>
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>936</v>
       </c>
@@ -2858,7 +2819,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>938</v>
       </c>
@@ -2869,7 +2830,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>940</v>
       </c>
@@ -2880,7 +2841,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>944</v>
       </c>
@@ -2891,7 +2852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>946</v>
       </c>
@@ -2902,7 +2863,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>947</v>
       </c>
@@ -2913,7 +2874,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>953</v>
       </c>
@@ -2924,7 +2885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>954</v>
       </c>
@@ -2935,7 +2896,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>959</v>
       </c>
@@ -2946,7 +2907,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>962</v>
       </c>
@@ -2957,7 +2918,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>965</v>
       </c>
@@ -2968,7 +2929,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>968</v>
       </c>
@@ -2979,7 +2940,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>970</v>
       </c>
@@ -2990,7 +2951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>983</v>
       </c>
@@ -3001,7 +2962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>993</v>
       </c>
@@ -3012,7 +2973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>997</v>
       </c>
@@ -3024,7 +2985,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="F3:L29" xr:uid="{F58841F4-1925-4FDA-9F67-00E3EE1323CD}"/>
+  <autoFilter ref="F3:L29" xr:uid="{F58841F4-1925-4FDA-9F67-00E3EE1323CD}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="0.666666667"/>
+        <filter val="1.333333333"/>
+        <filter val="1.666666667"/>
+        <filter val="2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>